--- a/artfynd/A 13578-2023 artfynd.xlsx
+++ b/artfynd/A 13578-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13578-2023 artfynd.xlsx
+++ b/artfynd/A 13578-2023 artfynd.xlsx
@@ -2039,11 +2039,11 @@
         <v>111528165</v>
       </c>
       <c r="B14" t="n">
-        <v>89845</v>
+        <v>91168</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521735.3223788696</v>
+        <v>521735</v>
       </c>
       <c r="R14" t="n">
-        <v>6933136.54926595</v>
+        <v>6933137</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>

--- a/artfynd/A 13578-2023 artfynd.xlsx
+++ b/artfynd/A 13578-2023 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>111529002</v>
       </c>
       <c r="B10" t="n">
-        <v>56398</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521751.8847309864</v>
+        <v>521751</v>
       </c>
       <c r="R10" t="n">
-        <v>6933007.843059707</v>
+        <v>6933008</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -3880,7 +3880,7 @@
         <v>111528470</v>
       </c>
       <c r="B30" t="n">
-        <v>56398</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521731.5804727955</v>
+        <v>521732</v>
       </c>
       <c r="R30" t="n">
-        <v>6933001.708009128</v>
+        <v>6933002</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>

--- a/artfynd/A 13578-2023 artfynd.xlsx
+++ b/artfynd/A 13578-2023 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>111529002</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>111528470</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 13578-2023 artfynd.xlsx
+++ b/artfynd/A 13578-2023 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>111529002</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>111528470</v>
       </c>
       <c r="B30" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
